--- a/단어DB.xlsx
+++ b/단어DB.xlsx
@@ -706,20 +706,30 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:07</t>
+        </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -838,20 +848,30 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:08</t>
+        </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -970,20 +990,30 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:06</t>
+        </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -1885,20 +1915,30 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:06</t>
+        </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -3054,17 +3094,27 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>오답</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:07</t>
+        </is>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>복습필요</t>
         </is>
       </c>
     </row>
@@ -3100,20 +3150,30 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:07</t>
+        </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -3188,20 +3248,30 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:06</t>
+        </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -3232,20 +3302,30 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:07</t>
+        </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -3462,20 +3542,30 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-05-15 19:49</t>
+        </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -4319,20 +4409,30 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:07</t>
+        </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -4735,13 +4835,13 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4750,11 +4850,11 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-05-15 17:16</t>
+          <t>2026-05-15 20:07</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -5665,20 +5765,30 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:07</t>
+        </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -6174,20 +6284,30 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:08</t>
+        </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -7025,20 +7145,30 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:08</t>
+        </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -8331,20 +8461,30 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:06</t>
+        </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -9026,20 +9166,30 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2026-05-15 19:49</t>
+        </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -9603,20 +9753,30 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:07</t>
+        </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -11107,20 +11267,30 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
       </c>
       <c r="I230" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>2026-05-15 19:49</t>
+        </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
@@ -12205,20 +12375,30 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>정답</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>2026-05-15 20:06</t>
+        </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>학습중</t>
         </is>
       </c>
     </row>
